--- a/verification/cases/roundtrip/formulas_datetime/init.xlsx
+++ b/verification/cases/roundtrip/formulas_datetime/init.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/dates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F12DF283-7B24-8345-89E2-F6AE9BF5DD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F9A68E4-2AFF-49A6-8634-13DF4D8389BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="660" windowWidth="28040" windowHeight="17180" xr2:uid="{63476466-BFCB-C04A-A60C-BF1759BA0DA4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{63476466-BFCB-C04A-A60C-BF1759BA0DA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1004,7 +1004,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1027,22 +1027,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC779502-69A0-7642-A385-E304023AA8DC}">
   <dimension ref="B2:M223"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="41.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="13" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="13" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1056,7 +1056,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
@@ -1070,7 +1070,7 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>45</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>46</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>47</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>45658</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>48</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>49</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>50</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>51</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>45808</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>52</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>53</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>45823.5</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>54</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>45823.604687500003</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>55</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>45920.344097222223</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>56</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
         <v>57</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -1201,7 +1201,7 @@
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="21" t="s">
         <v>58</v>
       </c>
@@ -1215,7 +1215,7 @@
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="22" t="s">
         <v>59</v>
       </c>
@@ -1223,61 +1223,61 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
         <v>61</v>
       </c>
       <c r="C21" s="24">
         <f ca="1">TODAY()</f>
-        <v>46062</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C22" s="25">
         <f ca="1">NOW()</f>
-        <v>46062.668717708337</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
+        <v>46275.595719444442</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C23" s="24">
         <f ca="1">TODAY()+1</f>
-        <v>46063</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
         <v>64</v>
       </c>
       <c r="C24" s="24">
         <f ca="1">TODAY()-1</f>
-        <v>46061</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
         <v>65</v>
       </c>
       <c r="C25" s="25">
         <f ca="1">NOW()+0.5</f>
-        <v>46063.168717708337</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
+        <v>46276.095719444442</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C26" s="26">
         <f ca="1">NOW()-TODAY()</f>
-        <v>0.66871770833677147</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
+        <v>0.59571944444178371</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
         <v>67</v>
       </c>
@@ -1286,52 +1286,52 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C28" s="27">
         <f ca="1">MONTH(TODAY())</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C29" s="27">
         <f ca="1">DAY(TODAY())</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="27">
         <f ca="1">HOUR(NOW())</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="27">
         <f ca="1">MINUTE(NOW())</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>72</v>
       </c>
       <c r="C32" s="27">
         <f ca="1">SECOND(NOW())</f>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -1345,7 +1345,7 @@
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -1359,7 +1359,7 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B35" s="21" t="s">
         <v>73</v>
       </c>
@@ -1373,7 +1373,7 @@
       <c r="J35" s="6"/>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B36" s="2" t="s">
         <v>74</v>
       </c>
@@ -1387,7 +1387,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B37" s="22" t="s">
         <v>75</v>
       </c>
@@ -1407,7 +1407,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
         <v>81</v>
       </c>
@@ -1421,15 +1421,15 @@
         <v>15</v>
       </c>
       <c r="F38" s="24">
-        <f>DATE(C38,D38,E38)</f>
+        <f t="shared" ref="F38:F53" si="0">DATE(C38,D38,E38)</f>
         <v>45823</v>
       </c>
       <c r="G38" s="23">
-        <f>IFERROR(INT(F38),"Error")</f>
+        <f t="shared" ref="G38:G53" si="1">IFERROR(INT(F38),"Error")</f>
         <v>45823</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
         <v>82</v>
       </c>
@@ -1443,15 +1443,15 @@
         <v>29</v>
       </c>
       <c r="F39" s="24">
-        <f>DATE(C39,D39,E39)</f>
+        <f t="shared" si="0"/>
         <v>45351</v>
       </c>
       <c r="G39" s="23">
-        <f>IFERROR(INT(F39),"Error")</f>
+        <f t="shared" si="1"/>
         <v>45351</v>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
         <v>83</v>
       </c>
@@ -1465,15 +1465,15 @@
         <v>28</v>
       </c>
       <c r="F40" s="24">
-        <f>DATE(C40,D40,E40)</f>
+        <f t="shared" si="0"/>
         <v>45716</v>
       </c>
       <c r="G40" s="23">
-        <f>IFERROR(INT(F40),"Error")</f>
+        <f t="shared" si="1"/>
         <v>45716</v>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
         <v>84</v>
       </c>
@@ -1487,15 +1487,15 @@
         <v>1</v>
       </c>
       <c r="F41" s="24">
-        <f>DATE(C41,D41,E41)</f>
+        <f t="shared" si="0"/>
         <v>45658</v>
       </c>
       <c r="G41" s="23">
-        <f>IFERROR(INT(F41),"Error")</f>
+        <f t="shared" si="1"/>
         <v>45658</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
         <v>85</v>
       </c>
@@ -1509,15 +1509,15 @@
         <v>31</v>
       </c>
       <c r="F42" s="24">
-        <f>DATE(C42,D42,E42)</f>
+        <f t="shared" si="0"/>
         <v>46022</v>
       </c>
       <c r="G42" s="23">
-        <f>IFERROR(INT(F42),"Error")</f>
+        <f t="shared" si="1"/>
         <v>46022</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
         <v>86</v>
       </c>
@@ -1531,15 +1531,15 @@
         <v>1</v>
       </c>
       <c r="F43" s="24">
-        <f>DATE(C43,D43,E43)</f>
+        <f t="shared" si="0"/>
         <v>46023</v>
       </c>
       <c r="G43" s="23">
-        <f>IFERROR(INT(F43),"Error")</f>
+        <f t="shared" si="1"/>
         <v>46023</v>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
         <v>87</v>
       </c>
@@ -1553,15 +1553,15 @@
         <v>1</v>
       </c>
       <c r="F44" s="24">
-        <f>DATE(C44,D44,E44)</f>
+        <f t="shared" si="0"/>
         <v>45627</v>
       </c>
       <c r="G44" s="23">
-        <f>IFERROR(INT(F44),"Error")</f>
+        <f t="shared" si="1"/>
         <v>45627</v>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
         <v>88</v>
       </c>
@@ -1575,15 +1575,15 @@
         <v>32</v>
       </c>
       <c r="F45" s="24">
-        <f>DATE(C45,D45,E45)</f>
+        <f t="shared" si="0"/>
         <v>45689</v>
       </c>
       <c r="G45" s="23">
-        <f>IFERROR(INT(F45),"Error")</f>
+        <f t="shared" si="1"/>
         <v>45689</v>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
         <v>89</v>
       </c>
@@ -1597,15 +1597,15 @@
         <v>0</v>
       </c>
       <c r="F46" s="24">
-        <f>DATE(C46,D46,E46)</f>
+        <f t="shared" si="0"/>
         <v>45657</v>
       </c>
       <c r="G46" s="23">
-        <f>IFERROR(INT(F46),"Error")</f>
+        <f t="shared" si="1"/>
         <v>45657</v>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
         <v>90</v>
       </c>
@@ -1619,15 +1619,15 @@
         <v>1</v>
       </c>
       <c r="F47" s="24">
-        <f>DATE(C47,D47,E47)</f>
+        <f t="shared" si="0"/>
         <v>45597</v>
       </c>
       <c r="G47" s="23">
-        <f>IFERROR(INT(F47),"Error")</f>
+        <f t="shared" si="1"/>
         <v>45597</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
         <v>91</v>
       </c>
@@ -1641,15 +1641,15 @@
         <v>-1</v>
       </c>
       <c r="F48" s="24">
-        <f>DATE(C48,D48,E48)</f>
+        <f t="shared" si="0"/>
         <v>45656</v>
       </c>
       <c r="G48" s="23">
-        <f>IFERROR(INT(F48),"Error")</f>
+        <f t="shared" si="1"/>
         <v>45656</v>
       </c>
     </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
         <v>92</v>
       </c>
@@ -1663,15 +1663,15 @@
         <v>1</v>
       </c>
       <c r="F49" s="24">
-        <f>DATE(C49,D49,E49)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G49" s="23">
-        <f>IFERROR(INT(F49),"Error")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.2">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
         <v>93</v>
       </c>
@@ -1685,15 +1685,15 @@
         <v>31</v>
       </c>
       <c r="F50" s="24">
-        <f>DATE(C50,D50,E50)</f>
+        <f t="shared" si="0"/>
         <v>2958465</v>
       </c>
       <c r="G50" s="23">
-        <f>IFERROR(INT(F50),"Error")</f>
+        <f t="shared" si="1"/>
         <v>2958465</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
         <v>94</v>
       </c>
@@ -1707,15 +1707,15 @@
         <v>1</v>
       </c>
       <c r="F51" s="24">
-        <f>DATE(C51,D51,E51)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G51" s="23">
-        <f>IFERROR(INT(F51),"Error")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.2">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
         <v>95</v>
       </c>
@@ -1729,15 +1729,15 @@
         <v>15</v>
       </c>
       <c r="F52" s="24">
-        <f>DATE(C52,D52,E52)</f>
+        <f t="shared" si="0"/>
         <v>9298</v>
       </c>
       <c r="G52" s="23">
-        <f>IFERROR(INT(F52),"Error")</f>
+        <f t="shared" si="1"/>
         <v>9298</v>
       </c>
     </row>
-    <row r="53" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
         <v>96</v>
       </c>
@@ -1751,15 +1751,15 @@
         <v>45</v>
       </c>
       <c r="F53" s="24">
-        <f>DATE(C53,D53,E53)</f>
+        <f t="shared" si="0"/>
         <v>46098</v>
       </c>
       <c r="G53" s="23">
-        <f>IFERROR(INT(F53),"Error")</f>
+        <f t="shared" si="1"/>
         <v>46098</v>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -1773,7 +1773,7 @@
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -1787,7 +1787,7 @@
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B56" s="21" t="s">
         <v>97</v>
       </c>
@@ -1801,7 +1801,7 @@
       <c r="J56" s="6"/>
       <c r="K56" s="6"/>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B57" s="22" t="s">
         <v>98</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B58" s="29" t="s">
         <v>100</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B59" s="29" t="s">
         <v>101</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B60" s="29" t="s">
         <v>102</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B61" s="29" t="s">
         <v>103</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B62" s="29" t="s">
         <v>104</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B63" s="29" t="s">
         <v>105</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B64" s="29" t="s">
         <v>106</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>45823</v>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B65" s="29" t="s">
         <v>107</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B66" s="29" t="s">
         <v>108</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>2958465</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B67" s="29" t="s">
         <v>109</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B68" s="29" t="s">
         <v>110</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>Error</v>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B69" s="29" t="s">
         <v>111</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>Error</v>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -1931,7 +1931,7 @@
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -1945,7 +1945,7 @@
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B72" s="30" t="s">
         <v>112</v>
       </c>
@@ -1959,7 +1959,7 @@
       <c r="J72" s="6"/>
       <c r="K72" s="6"/>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B73" s="22" t="s">
         <v>20</v>
       </c>
@@ -1973,9 +1973,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B74" s="4" t="str">
-        <f>B5</f>
+        <f t="shared" ref="B74:B86" si="2">B5</f>
         <v>Regular Date</v>
       </c>
       <c r="C74" s="23">
@@ -1991,9 +1991,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B75" s="4" t="str">
-        <f>B6</f>
+        <f t="shared" si="2"/>
         <v>Leap Year Date</v>
       </c>
       <c r="C75" s="23">
@@ -2009,9 +2009,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B76" s="4" t="str">
-        <f>B7</f>
+        <f t="shared" si="2"/>
         <v>Year Start</v>
       </c>
       <c r="C76" s="23">
@@ -2027,9 +2027,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B77" s="4" t="str">
-        <f>B8</f>
+        <f t="shared" si="2"/>
         <v>Year End</v>
       </c>
       <c r="C77" s="23">
@@ -2045,9 +2045,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="str">
-        <f>B9</f>
+        <f t="shared" si="2"/>
         <v>Month Start</v>
       </c>
       <c r="C78" s="23">
@@ -2063,9 +2063,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B79" s="4" t="str">
-        <f>B10</f>
+        <f t="shared" si="2"/>
         <v>Month End (30)</v>
       </c>
       <c r="C79" s="23">
@@ -2081,9 +2081,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B80" s="4" t="str">
-        <f>B11</f>
+        <f t="shared" si="2"/>
         <v>Month End (31)</v>
       </c>
       <c r="C80" s="23">
@@ -2099,9 +2099,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B81" s="4" t="str">
-        <f>B12</f>
+        <f t="shared" si="2"/>
         <v>Time Midnight</v>
       </c>
       <c r="C81" s="23">
@@ -2117,9 +2117,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B82" s="4" t="str">
-        <f>B13</f>
+        <f t="shared" si="2"/>
         <v>Time Midday</v>
       </c>
       <c r="C82" s="23">
@@ -2135,9 +2135,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B83" s="4" t="str">
-        <f>B14</f>
+        <f t="shared" si="2"/>
         <v>Time Full</v>
       </c>
       <c r="C83" s="23">
@@ -2153,9 +2153,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B84" s="4" t="str">
-        <f>B15</f>
+        <f t="shared" si="2"/>
         <v>Date-Time Combo</v>
       </c>
       <c r="C84" s="23">
@@ -2171,9 +2171,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B85" s="4" t="str">
-        <f>B16</f>
+        <f t="shared" si="2"/>
         <v>Far Past Date</v>
       </c>
       <c r="C85" s="23">
@@ -2189,9 +2189,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B86" s="4" t="str">
-        <f>B17</f>
+        <f t="shared" si="2"/>
         <v>Far Future Date</v>
       </c>
       <c r="C86" s="23">
@@ -2207,7 +2207,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
@@ -2221,7 +2221,7 @@
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
     </row>
-    <row r="88" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
@@ -2235,7 +2235,7 @@
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
     </row>
-    <row r="89" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B89" s="6" t="s">
         <v>116</v>
       </c>
@@ -2249,7 +2249,7 @@
       <c r="J89" s="6"/>
       <c r="K89" s="6"/>
     </row>
-    <row r="90" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B90" s="22" t="s">
         <v>20</v>
       </c>
@@ -2263,9 +2263,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="91" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B91" s="4" t="str">
-        <f>B5</f>
+        <f t="shared" ref="B91:B103" si="3">B5</f>
         <v>Regular Date</v>
       </c>
       <c r="C91" s="23">
@@ -2281,9 +2281,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B92" s="4" t="str">
-        <f>B6</f>
+        <f t="shared" si="3"/>
         <v>Leap Year Date</v>
       </c>
       <c r="C92" s="23">
@@ -2299,9 +2299,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B93" s="4" t="str">
-        <f>B7</f>
+        <f t="shared" si="3"/>
         <v>Year Start</v>
       </c>
       <c r="C93" s="23">
@@ -2317,9 +2317,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B94" s="4" t="str">
-        <f>B8</f>
+        <f t="shared" si="3"/>
         <v>Year End</v>
       </c>
       <c r="C94" s="23">
@@ -2335,9 +2335,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B95" s="4" t="str">
-        <f>B9</f>
+        <f t="shared" si="3"/>
         <v>Month Start</v>
       </c>
       <c r="C95" s="23">
@@ -2353,9 +2353,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B96" s="4" t="str">
-        <f>B10</f>
+        <f t="shared" si="3"/>
         <v>Month End (30)</v>
       </c>
       <c r="C96" s="23">
@@ -2371,9 +2371,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B97" s="4" t="str">
-        <f>B11</f>
+        <f t="shared" si="3"/>
         <v>Month End (31)</v>
       </c>
       <c r="C97" s="23">
@@ -2389,9 +2389,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B98" s="4" t="str">
-        <f>B12</f>
+        <f t="shared" si="3"/>
         <v>Time Midnight</v>
       </c>
       <c r="C98" s="23">
@@ -2407,9 +2407,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B99" s="4" t="str">
-        <f>B13</f>
+        <f t="shared" si="3"/>
         <v>Time Midday</v>
       </c>
       <c r="C99" s="23">
@@ -2425,9 +2425,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B100" s="4" t="str">
-        <f>B14</f>
+        <f t="shared" si="3"/>
         <v>Time Full</v>
       </c>
       <c r="C100" s="23">
@@ -2443,9 +2443,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="101" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B101" s="4" t="str">
-        <f>B15</f>
+        <f t="shared" si="3"/>
         <v>Date-Time Combo</v>
       </c>
       <c r="C101" s="23">
@@ -2461,9 +2461,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="102" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B102" s="4" t="str">
-        <f>B16</f>
+        <f t="shared" si="3"/>
         <v>Far Past Date</v>
       </c>
       <c r="C102" s="23">
@@ -2479,9 +2479,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B103" s="4" t="str">
-        <f>B17</f>
+        <f t="shared" si="3"/>
         <v>Far Future Date</v>
       </c>
       <c r="C103" s="23">
@@ -2497,7 +2497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
@@ -2511,7 +2511,7 @@
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
     </row>
-    <row r="105" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
@@ -2525,7 +2525,7 @@
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
     </row>
-    <row r="106" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B106" s="6" t="s">
         <v>120</v>
       </c>
@@ -2539,7 +2539,7 @@
       <c r="J106" s="6"/>
       <c r="K106" s="6"/>
     </row>
-    <row r="107" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B107" s="22" t="s">
         <v>121</v>
       </c>
@@ -2574,9 +2574,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="108" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B108" s="4" t="str">
-        <f>B5</f>
+        <f t="shared" ref="B108:B120" si="4">B5</f>
         <v>Regular Date</v>
       </c>
       <c r="C108" s="23">
@@ -2620,9 +2620,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B109" s="4" t="str">
-        <f>B6</f>
+        <f t="shared" si="4"/>
         <v>Leap Year Date</v>
       </c>
       <c r="C109" s="23">
@@ -2666,9 +2666,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B110" s="4" t="str">
-        <f>B7</f>
+        <f t="shared" si="4"/>
         <v>Year Start</v>
       </c>
       <c r="C110" s="23">
@@ -2712,9 +2712,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B111" s="4" t="str">
-        <f>B8</f>
+        <f t="shared" si="4"/>
         <v>Year End</v>
       </c>
       <c r="C111" s="23">
@@ -2758,9 +2758,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B112" s="4" t="str">
-        <f>B9</f>
+        <f t="shared" si="4"/>
         <v>Month Start</v>
       </c>
       <c r="C112" s="23">
@@ -2804,9 +2804,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B113" s="4" t="str">
-        <f>B10</f>
+        <f t="shared" si="4"/>
         <v>Month End (30)</v>
       </c>
       <c r="C113" s="23">
@@ -2850,9 +2850,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B114" s="4" t="str">
-        <f>B11</f>
+        <f t="shared" si="4"/>
         <v>Month End (31)</v>
       </c>
       <c r="C114" s="23">
@@ -2896,9 +2896,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B115" s="4" t="str">
-        <f>B12</f>
+        <f t="shared" si="4"/>
         <v>Time Midnight</v>
       </c>
       <c r="C115" s="23">
@@ -2942,9 +2942,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B116" s="4" t="str">
-        <f>B13</f>
+        <f t="shared" si="4"/>
         <v>Time Midday</v>
       </c>
       <c r="C116" s="23">
@@ -2988,9 +2988,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B117" s="4" t="str">
-        <f>B14</f>
+        <f t="shared" si="4"/>
         <v>Time Full</v>
       </c>
       <c r="C117" s="23">
@@ -3034,9 +3034,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B118" s="4" t="str">
-        <f>B15</f>
+        <f t="shared" si="4"/>
         <v>Date-Time Combo</v>
       </c>
       <c r="C118" s="23">
@@ -3080,9 +3080,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B119" s="4" t="str">
-        <f>B16</f>
+        <f t="shared" si="4"/>
         <v>Far Past Date</v>
       </c>
       <c r="C119" s="23">
@@ -3126,9 +3126,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B120" s="4" t="str">
-        <f>B17</f>
+        <f t="shared" si="4"/>
         <v>Far Future Date</v>
       </c>
       <c r="C120" s="23">
@@ -3172,7 +3172,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
@@ -3186,7 +3186,7 @@
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
     </row>
-    <row r="122" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
@@ -3200,7 +3200,7 @@
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
     </row>
-    <row r="123" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B123" s="6" t="s">
         <v>122</v>
       </c>
@@ -3214,7 +3214,7 @@
       <c r="J123" s="6"/>
       <c r="K123" s="6"/>
     </row>
-    <row r="124" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B124" s="22" t="s">
         <v>121</v>
       </c>
@@ -3249,9 +3249,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="125" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B125" s="4" t="str">
-        <f>B5</f>
+        <f t="shared" ref="B125:B137" si="5">B5</f>
         <v>Regular Date</v>
       </c>
       <c r="C125" s="23">
@@ -3295,9 +3295,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="126" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B126" s="4" t="str">
-        <f>B6</f>
+        <f t="shared" si="5"/>
         <v>Leap Year Date</v>
       </c>
       <c r="C126" s="23">
@@ -3341,9 +3341,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B127" s="4" t="str">
-        <f>B7</f>
+        <f t="shared" si="5"/>
         <v>Year Start</v>
       </c>
       <c r="C127" s="23">
@@ -3387,9 +3387,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B128" s="4" t="str">
-        <f>B8</f>
+        <f t="shared" si="5"/>
         <v>Year End</v>
       </c>
       <c r="C128" s="23">
@@ -3433,9 +3433,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B129" s="4" t="str">
-        <f>B9</f>
+        <f t="shared" si="5"/>
         <v>Month Start</v>
       </c>
       <c r="C129" s="23">
@@ -3479,9 +3479,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B130" s="4" t="str">
-        <f>B10</f>
+        <f t="shared" si="5"/>
         <v>Month End (30)</v>
       </c>
       <c r="C130" s="23">
@@ -3525,9 +3525,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B131" s="4" t="str">
-        <f>B11</f>
+        <f t="shared" si="5"/>
         <v>Month End (31)</v>
       </c>
       <c r="C131" s="23">
@@ -3571,9 +3571,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="132" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B132" s="4" t="str">
-        <f>B12</f>
+        <f t="shared" si="5"/>
         <v>Time Midnight</v>
       </c>
       <c r="C132" s="23">
@@ -3617,9 +3617,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="133" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B133" s="4" t="str">
-        <f>B13</f>
+        <f t="shared" si="5"/>
         <v>Time Midday</v>
       </c>
       <c r="C133" s="23">
@@ -3663,9 +3663,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="134" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B134" s="4" t="str">
-        <f>B14</f>
+        <f t="shared" si="5"/>
         <v>Time Full</v>
       </c>
       <c r="C134" s="23">
@@ -3709,9 +3709,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="135" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B135" s="4" t="str">
-        <f>B15</f>
+        <f t="shared" si="5"/>
         <v>Date-Time Combo</v>
       </c>
       <c r="C135" s="23">
@@ -3755,9 +3755,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="136" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B136" s="4" t="str">
-        <f>B16</f>
+        <f t="shared" si="5"/>
         <v>Far Past Date</v>
       </c>
       <c r="C136" s="23">
@@ -3801,9 +3801,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="137" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B137" s="4" t="str">
-        <f>B17</f>
+        <f t="shared" si="5"/>
         <v>Far Future Date</v>
       </c>
       <c r="C137" s="23">
@@ -3847,7 +3847,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="138" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
@@ -3861,7 +3861,7 @@
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
     </row>
-    <row r="139" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
@@ -3875,7 +3875,7 @@
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
     </row>
-    <row r="140" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B140" s="6" t="s">
         <v>123</v>
       </c>
@@ -3889,7 +3889,7 @@
       <c r="J140" s="6"/>
       <c r="K140" s="6"/>
     </row>
-    <row r="141" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B141" s="22" t="s">
         <v>124</v>
       </c>
@@ -3924,9 +3924,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="142" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B142" s="4" t="str">
-        <f>B5</f>
+        <f t="shared" ref="B142:B154" si="6">B5</f>
         <v>Regular Date</v>
       </c>
       <c r="C142" s="24">
@@ -3970,9 +3970,9 @@
         <v>46553</v>
       </c>
     </row>
-    <row r="143" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B143" s="4" t="str">
-        <f>B6</f>
+        <f t="shared" si="6"/>
         <v>Leap Year Date</v>
       </c>
       <c r="C143" s="24">
@@ -4016,9 +4016,9 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="144" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B144" s="4" t="str">
-        <f>B7</f>
+        <f t="shared" si="6"/>
         <v>Year Start</v>
       </c>
       <c r="C144" s="24">
@@ -4062,9 +4062,9 @@
         <v>46388</v>
       </c>
     </row>
-    <row r="145" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B145" s="4" t="str">
-        <f>B8</f>
+        <f t="shared" si="6"/>
         <v>Year End</v>
       </c>
       <c r="C145" s="24">
@@ -4108,9 +4108,9 @@
         <v>46752</v>
       </c>
     </row>
-    <row r="146" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B146" s="4" t="str">
-        <f>B9</f>
+        <f t="shared" si="6"/>
         <v>Month Start</v>
       </c>
       <c r="C146" s="24">
@@ -4154,9 +4154,9 @@
         <v>46447</v>
       </c>
     </row>
-    <row r="147" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B147" s="4" t="str">
-        <f>B10</f>
+        <f t="shared" si="6"/>
         <v>Month End (30)</v>
       </c>
       <c r="C147" s="24">
@@ -4200,9 +4200,9 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="148" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B148" s="4" t="str">
-        <f>B11</f>
+        <f t="shared" si="6"/>
         <v>Month End (31)</v>
       </c>
       <c r="C148" s="24">
@@ -4246,9 +4246,9 @@
         <v>46538</v>
       </c>
     </row>
-    <row r="149" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B149" s="4" t="str">
-        <f>B12</f>
+        <f t="shared" si="6"/>
         <v>Time Midnight</v>
       </c>
       <c r="C149" s="24">
@@ -4292,9 +4292,9 @@
         <v>46553</v>
       </c>
     </row>
-    <row r="150" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B150" s="4" t="str">
-        <f>B13</f>
+        <f t="shared" si="6"/>
         <v>Time Midday</v>
       </c>
       <c r="C150" s="24">
@@ -4338,9 +4338,9 @@
         <v>46553</v>
       </c>
     </row>
-    <row r="151" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B151" s="4" t="str">
-        <f>B14</f>
+        <f t="shared" si="6"/>
         <v>Time Full</v>
       </c>
       <c r="C151" s="24">
@@ -4384,9 +4384,9 @@
         <v>46553</v>
       </c>
     </row>
-    <row r="152" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B152" s="4" t="str">
-        <f>B15</f>
+        <f t="shared" si="6"/>
         <v>Date-Time Combo</v>
       </c>
       <c r="C152" s="24">
@@ -4430,9 +4430,9 @@
         <v>46650</v>
       </c>
     </row>
-    <row r="153" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B153" s="4" t="str">
-        <f>B16</f>
+        <f t="shared" si="6"/>
         <v>Far Past Date</v>
       </c>
       <c r="C153" s="24" t="str">
@@ -4476,9 +4476,9 @@
         <v>732</v>
       </c>
     </row>
-    <row r="154" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B154" s="4" t="str">
-        <f>B17</f>
+        <f t="shared" si="6"/>
         <v>Far Future Date</v>
       </c>
       <c r="C154" s="24">
@@ -4522,7 +4522,7 @@
         <v>73780</v>
       </c>
     </row>
-    <row r="155" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
@@ -4536,7 +4536,7 @@
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
     </row>
-    <row r="156" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
@@ -4550,7 +4550,7 @@
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
     </row>
-    <row r="157" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B157" s="6" t="s">
         <v>125</v>
       </c>
@@ -4564,7 +4564,7 @@
       <c r="J157" s="6"/>
       <c r="K157" s="6"/>
     </row>
-    <row r="158" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B158" s="22" t="s">
         <v>124</v>
       </c>
@@ -4599,9 +4599,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="159" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B159" s="4" t="str">
-        <f>B5</f>
+        <f t="shared" ref="B159:B171" si="7">B5</f>
         <v>Regular Date</v>
       </c>
       <c r="C159" s="24">
@@ -4645,9 +4645,9 @@
         <v>46568</v>
       </c>
     </row>
-    <row r="160" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B160" s="4" t="str">
-        <f>B6</f>
+        <f t="shared" si="7"/>
         <v>Leap Year Date</v>
       </c>
       <c r="C160" s="24">
@@ -4691,9 +4691,9 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="161" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B161" s="4" t="str">
-        <f>B7</f>
+        <f t="shared" si="7"/>
         <v>Year Start</v>
       </c>
       <c r="C161" s="24">
@@ -4737,9 +4737,9 @@
         <v>46418</v>
       </c>
     </row>
-    <row r="162" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B162" s="4" t="str">
-        <f>B8</f>
+        <f t="shared" si="7"/>
         <v>Year End</v>
       </c>
       <c r="C162" s="24">
@@ -4783,9 +4783,9 @@
         <v>46752</v>
       </c>
     </row>
-    <row r="163" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B163" s="4" t="str">
-        <f>B9</f>
+        <f t="shared" si="7"/>
         <v>Month Start</v>
       </c>
       <c r="C163" s="24">
@@ -4829,9 +4829,9 @@
         <v>46477</v>
       </c>
     </row>
-    <row r="164" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B164" s="4" t="str">
-        <f>B10</f>
+        <f t="shared" si="7"/>
         <v>Month End (30)</v>
       </c>
       <c r="C164" s="24">
@@ -4875,9 +4875,9 @@
         <v>46507</v>
       </c>
     </row>
-    <row r="165" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B165" s="4" t="str">
-        <f>B11</f>
+        <f t="shared" si="7"/>
         <v>Month End (31)</v>
       </c>
       <c r="C165" s="24">
@@ -4921,9 +4921,9 @@
         <v>46538</v>
       </c>
     </row>
-    <row r="166" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B166" s="4" t="str">
-        <f>B12</f>
+        <f t="shared" si="7"/>
         <v>Time Midnight</v>
       </c>
       <c r="C166" s="24">
@@ -4967,9 +4967,9 @@
         <v>46568</v>
       </c>
     </row>
-    <row r="167" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B167" s="4" t="str">
-        <f>B13</f>
+        <f t="shared" si="7"/>
         <v>Time Midday</v>
       </c>
       <c r="C167" s="24">
@@ -5013,9 +5013,9 @@
         <v>46568</v>
       </c>
     </row>
-    <row r="168" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="168" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B168" s="4" t="str">
-        <f>B14</f>
+        <f t="shared" si="7"/>
         <v>Time Full</v>
       </c>
       <c r="C168" s="24">
@@ -5059,9 +5059,9 @@
         <v>46568</v>
       </c>
     </row>
-    <row r="169" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B169" s="4" t="str">
-        <f>B15</f>
+        <f t="shared" si="7"/>
         <v>Date-Time Combo</v>
       </c>
       <c r="C169" s="24">
@@ -5105,9 +5105,9 @@
         <v>46660</v>
       </c>
     </row>
-    <row r="170" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B170" s="4" t="str">
-        <f>B16</f>
+        <f t="shared" si="7"/>
         <v>Far Past Date</v>
       </c>
       <c r="C170" s="24" t="str">
@@ -5151,9 +5151,9 @@
         <v>762</v>
       </c>
     </row>
-    <row r="171" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B171" s="4" t="str">
-        <f>B17</f>
+        <f t="shared" si="7"/>
         <v>Far Future Date</v>
       </c>
       <c r="C171" s="24">
@@ -5197,7 +5197,7 @@
         <v>73780</v>
       </c>
     </row>
-    <row r="172" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
@@ -5211,7 +5211,7 @@
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
     </row>
-    <row r="173" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
@@ -5225,7 +5225,7 @@
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
     </row>
-    <row r="174" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B174" s="6" t="s">
         <v>126</v>
       </c>
@@ -5239,7 +5239,7 @@
       <c r="J174" s="6"/>
       <c r="K174" s="6"/>
     </row>
-    <row r="175" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="175" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B175" s="22" t="s">
         <v>127</v>
       </c>
@@ -5271,9 +5271,9 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="176" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B176" s="4" t="str">
-        <f>B5</f>
+        <f t="shared" ref="B176:B182" si="8">B5</f>
         <v>Regular Date</v>
       </c>
       <c r="C176" s="23">
@@ -5313,9 +5313,9 @@
         <v>19449</v>
       </c>
     </row>
-    <row r="177" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B177" s="4" t="str">
-        <f>B6</f>
+        <f t="shared" si="8"/>
         <v>Leap Year Date</v>
       </c>
       <c r="C177" s="23">
@@ -5355,9 +5355,9 @@
         <v>19786</v>
       </c>
     </row>
-    <row r="178" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B178" s="4" t="str">
-        <f>B7</f>
+        <f t="shared" si="8"/>
         <v>Year Start</v>
       </c>
       <c r="C178" s="23">
@@ -5397,9 +5397,9 @@
         <v>19567</v>
       </c>
     </row>
-    <row r="179" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B179" s="4" t="str">
-        <f>B8</f>
+        <f t="shared" si="8"/>
         <v>Year End</v>
       </c>
       <c r="C179" s="23">
@@ -5439,9 +5439,9 @@
         <v>19307</v>
       </c>
     </row>
-    <row r="180" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B180" s="4" t="str">
-        <f>B9</f>
+        <f t="shared" si="8"/>
         <v>Month Start</v>
       </c>
       <c r="C180" s="23">
@@ -5481,9 +5481,9 @@
         <v>19524</v>
       </c>
     </row>
-    <row r="181" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B181" s="4" t="str">
-        <f>B10</f>
+        <f t="shared" si="8"/>
         <v>Month End (30)</v>
       </c>
       <c r="C181" s="23">
@@ -5523,9 +5523,9 @@
         <v>19482</v>
       </c>
     </row>
-    <row r="182" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B182" s="4" t="str">
-        <f>B11</f>
+        <f t="shared" si="8"/>
         <v>Month End (31)</v>
       </c>
       <c r="C182" s="23">
@@ -5565,7 +5565,7 @@
         <v>19459</v>
       </c>
     </row>
-    <row r="183" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B183" s="4" t="str">
         <f>B16</f>
         <v>Far Past Date</v>
@@ -5607,7 +5607,7 @@
         <v>52179</v>
       </c>
     </row>
-    <row r="184" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B184" s="4" t="str">
         <f>B17</f>
         <v>Far Future Date</v>
@@ -5649,7 +5649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
@@ -5663,7 +5663,7 @@
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
     </row>
-    <row r="186" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
@@ -5677,7 +5677,7 @@
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
     </row>
-    <row r="187" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B187" s="6" t="s">
         <v>128</v>
       </c>
@@ -5691,7 +5691,7 @@
       <c r="J187" s="6"/>
       <c r="K187" s="6"/>
     </row>
-    <row r="188" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B188" s="22" t="s">
         <v>129</v>
       </c>
@@ -5729,9 +5729,9 @@
         <v>252</v>
       </c>
     </row>
-    <row r="189" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="189" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B189" s="4" t="str">
-        <f>B5</f>
+        <f t="shared" ref="B189:B195" si="9">B5</f>
         <v>Regular Date</v>
       </c>
       <c r="C189" s="24">
@@ -5779,9 +5779,9 @@
         <v>46175</v>
       </c>
     </row>
-    <row r="190" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="190" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B190" s="4" t="str">
-        <f>B6</f>
+        <f t="shared" si="9"/>
         <v>Leap Year Date</v>
       </c>
       <c r="C190" s="24">
@@ -5829,9 +5829,9 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="191" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B191" s="4" t="str">
-        <f>B7</f>
+        <f t="shared" si="9"/>
         <v>Year Start</v>
       </c>
       <c r="C191" s="24">
@@ -5879,9 +5879,9 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="192" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B192" s="4" t="str">
-        <f>B8</f>
+        <f t="shared" si="9"/>
         <v>Year End</v>
       </c>
       <c r="C192" s="24">
@@ -5929,9 +5929,9 @@
         <v>46374</v>
       </c>
     </row>
-    <row r="193" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B193" s="4" t="str">
-        <f>B9</f>
+        <f t="shared" si="9"/>
         <v>Month Start</v>
       </c>
       <c r="C193" s="24">
@@ -5979,9 +5979,9 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="194" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B194" s="4" t="str">
-        <f>B10</f>
+        <f t="shared" si="9"/>
         <v>Month End (30)</v>
       </c>
       <c r="C194" s="24">
@@ -6029,9 +6029,9 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="195" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="195" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B195" s="4" t="str">
-        <f>B11</f>
+        <f t="shared" si="9"/>
         <v>Month End (31)</v>
       </c>
       <c r="C195" s="24">
@@ -6079,7 +6079,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="196" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="196" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B196" s="4" t="str">
         <f>B16</f>
         <v>Far Past Date</v>
@@ -6129,7 +6129,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="197" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="197" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B197" s="4" t="str">
         <f>B17</f>
         <v>Far Future Date</v>
@@ -6179,7 +6179,7 @@
         <v>73404</v>
       </c>
     </row>
-    <row r="198" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="198" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
@@ -6193,7 +6193,7 @@
       <c r="L198" s="2"/>
       <c r="M198" s="2"/>
     </row>
-    <row r="199" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="199" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
@@ -6207,7 +6207,7 @@
       <c r="L199" s="2"/>
       <c r="M199" s="2"/>
     </row>
-    <row r="200" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="200" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B200" s="6" t="s">
         <v>130</v>
       </c>
@@ -6221,7 +6221,7 @@
       <c r="J200" s="6"/>
       <c r="K200" s="6"/>
     </row>
-    <row r="201" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="201" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B201" s="22" t="s">
         <v>131</v>
       </c>
@@ -6247,7 +6247,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="202" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="202" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B202" s="32">
         <f>C5</f>
         <v>45823</v>
@@ -6281,7 +6281,7 @@
         <v>Error</v>
       </c>
     </row>
-    <row r="203" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="203" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B203" s="32">
         <f>C7</f>
         <v>45658</v>
@@ -6315,7 +6315,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="204" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="204" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B204" s="32">
         <f>C7</f>
         <v>45658</v>
@@ -6349,7 +6349,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="205" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="205" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B205" s="32">
         <f>C6</f>
         <v>45351</v>
@@ -6383,7 +6383,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="206" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="206" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B206" s="32">
         <f>C16</f>
         <v>1</v>
@@ -6417,7 +6417,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="207" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="207" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B207" s="32">
         <f>C7</f>
         <v>45658</v>
@@ -6451,7 +6451,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="208" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="208" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B208" s="32">
         <f>C9</f>
         <v>45717</v>
@@ -6485,7 +6485,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="209" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="209" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B209" s="32">
         <f>C10</f>
         <v>45777</v>
@@ -6519,7 +6519,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="210" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="210" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B210" s="32">
         <f>C5</f>
         <v>45823</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="211" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
       <c r="D211" s="2"/>
@@ -6567,7 +6567,7 @@
       <c r="L211" s="2"/>
       <c r="M211" s="2"/>
     </row>
-    <row r="212" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="212" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
@@ -6581,7 +6581,7 @@
       <c r="L212" s="2"/>
       <c r="M212" s="2"/>
     </row>
-    <row r="213" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="213" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B213" s="6" t="s">
         <v>139</v>
       </c>
@@ -6595,7 +6595,7 @@
       <c r="J213" s="6"/>
       <c r="K213" s="6"/>
     </row>
-    <row r="214" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="214" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B214" s="22" t="s">
         <v>127</v>
       </c>
@@ -6627,9 +6627,9 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="215" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="215" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B215" s="4" t="str">
-        <f>B5</f>
+        <f t="shared" ref="B215:B221" si="10">B5</f>
         <v>Regular Date</v>
       </c>
       <c r="C215" s="23">
@@ -6669,9 +6669,9 @@
         <v>27227</v>
       </c>
     </row>
-    <row r="216" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="216" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B216" s="4" t="str">
-        <f>B6</f>
+        <f t="shared" si="10"/>
         <v>Leap Year Date</v>
       </c>
       <c r="C216" s="23">
@@ -6711,9 +6711,9 @@
         <v>27699</v>
       </c>
     </row>
-    <row r="217" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="217" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B217" s="4" t="str">
-        <f>B7</f>
+        <f t="shared" si="10"/>
         <v>Year Start</v>
       </c>
       <c r="C217" s="23">
@@ -6753,9 +6753,9 @@
         <v>27392</v>
       </c>
     </row>
-    <row r="218" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="218" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B218" s="4" t="str">
-        <f>B8</f>
+        <f t="shared" si="10"/>
         <v>Year End</v>
       </c>
       <c r="C218" s="23">
@@ -6795,9 +6795,9 @@
         <v>27028</v>
       </c>
     </row>
-    <row r="219" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="219" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B219" s="4" t="str">
-        <f>B9</f>
+        <f t="shared" si="10"/>
         <v>Month Start</v>
       </c>
       <c r="C219" s="23">
@@ -6837,9 +6837,9 @@
         <v>27333</v>
       </c>
     </row>
-    <row r="220" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="220" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B220" s="4" t="str">
-        <f>B10</f>
+        <f t="shared" si="10"/>
         <v>Month End (30)</v>
       </c>
       <c r="C220" s="23">
@@ -6879,9 +6879,9 @@
         <v>27273</v>
       </c>
     </row>
-    <row r="221" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="221" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B221" s="4" t="str">
-        <f>B11</f>
+        <f t="shared" si="10"/>
         <v>Month End (31)</v>
       </c>
       <c r="C221" s="23">
@@ -6921,7 +6921,7 @@
         <v>27242</v>
       </c>
     </row>
-    <row r="222" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="222" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B222" s="4" t="str">
         <f>B16</f>
         <v>Far Past Date</v>
@@ -6963,7 +6963,7 @@
         <v>73049</v>
       </c>
     </row>
-    <row r="223" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="223" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B223" s="4" t="str">
         <f>B17</f>
         <v>Far Future Date</v>
@@ -7013,13 +7013,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{772B25B9-F50B-AE40-BD47-907F981C9C3C}">
   <dimension ref="B2:K1176"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -7033,7 +7033,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -7045,7 +7045,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
@@ -7059,7 +7059,7 @@
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -7075,7 +7075,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -7091,7 +7091,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
@@ -7107,7 +7107,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
@@ -7123,7 +7123,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -7139,7 +7139,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
@@ -7156,7 +7156,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
@@ -7173,7 +7173,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
         <v>9</v>
       </c>
@@ -7190,7 +7190,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
         <v>10</v>
       </c>
@@ -7207,7 +7207,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -7219,7 +7219,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -7231,7 +7231,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="6" t="s">
         <v>11</v>
       </c>
@@ -7245,7 +7245,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
         <v>12</v>
       </c>
@@ -7277,7 +7277,7 @@
         <v>-9.990000000000001E+307</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="10">
         <v>0</v>
       </c>
@@ -7318,7 +7318,7 @@
         <v>-9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="10">
         <v>1</v>
       </c>
@@ -7359,7 +7359,7 @@
         <v>-9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="10">
         <v>-1</v>
       </c>
@@ -7400,7 +7400,7 @@
         <v>-9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="10">
         <v>42.5</v>
       </c>
@@ -7441,7 +7441,7 @@
         <v>-9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="10">
         <v>-42.5</v>
       </c>
@@ -7482,7 +7482,7 @@
         <v>-9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="12">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -7523,7 +7523,7 @@
         <v>-9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="12">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -7564,7 +7564,7 @@
         <v>-9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="12">
         <v>9.990000000000001E+307</v>
       </c>
@@ -7605,7 +7605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="12">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -7646,7 +7646,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -7658,7 +7658,7 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -7670,7 +7670,7 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="6" t="s">
         <v>13</v>
       </c>
@@ -7684,7 +7684,7 @@
       <c r="J29" s="6"/>
       <c r="K29" s="6"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="7" t="s">
         <v>12</v>
       </c>
@@ -7716,7 +7716,7 @@
         <v>-9.990000000000001E+307</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="10">
         <v>0</v>
       </c>
@@ -7757,7 +7757,7 @@
         <v>9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="10">
         <v>1</v>
       </c>
@@ -7798,7 +7798,7 @@
         <v>9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="10">
         <v>-1</v>
       </c>
@@ -7839,7 +7839,7 @@
         <v>9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="10">
         <v>42.5</v>
       </c>
@@ -7880,7 +7880,7 @@
         <v>9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="10">
         <v>-42.5</v>
       </c>
@@ -7921,7 +7921,7 @@
         <v>9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" s="12">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -7962,7 +7962,7 @@
         <v>9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" s="12">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" s="12">
         <v>9.990000000000001E+307</v>
       </c>
@@ -8044,7 +8044,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39" s="12">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -8097,7 +8097,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -8109,7 +8109,7 @@
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="6" t="s">
         <v>14</v>
       </c>
@@ -8123,7 +8123,7 @@
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B43" s="7" t="s">
         <v>12</v>
       </c>
@@ -8155,7 +8155,7 @@
         <v>-9.990000000000001E+307</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="10">
         <v>0</v>
       </c>
@@ -8196,7 +8196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B45" s="10">
         <v>1</v>
       </c>
@@ -8237,7 +8237,7 @@
         <v>-9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="10">
         <v>-1</v>
       </c>
@@ -8278,7 +8278,7 @@
         <v>9.9999999999999901E+307</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B47" s="10">
         <v>42.5</v>
       </c>
@@ -8319,7 +8319,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B48" s="10">
         <v>-42.5</v>
       </c>
@@ -8360,7 +8360,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B49" s="12">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -8401,7 +8401,7 @@
         <v>-9.9999999999999911</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B50" s="12">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -8442,7 +8442,7 @@
         <v>9.9999999999999858</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B51" s="12">
         <v>9.990000000000001E+307</v>
       </c>
@@ -8483,7 +8483,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B52" s="12">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -8524,7 +8524,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -8536,7 +8536,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -8548,7 +8548,7 @@
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
     </row>
-    <row r="55" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="6" t="s">
         <v>15</v>
       </c>
@@ -8562,7 +8562,7 @@
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B56" s="7" t="s">
         <v>12</v>
       </c>
@@ -8594,7 +8594,7 @@
         <v>-9.990000000000001E+307</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B57" s="10">
         <v>0</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B58" s="10">
         <v>1</v>
       </c>
@@ -8676,7 +8676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B59" s="10">
         <v>-1</v>
       </c>
@@ -8717,7 +8717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B60" s="10">
         <v>42.5</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>-4.2500000000000045E-307</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B61" s="10">
         <v>-42.5</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>4.2500000000000045E-307</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B62" s="12">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -8840,7 +8840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B63" s="12">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -8881,7 +8881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B64" s="12">
         <v>9.990000000000001E+307</v>
       </c>
@@ -8922,7 +8922,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B65" s="12">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -8963,7 +8963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -8975,7 +8975,7 @@
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -8987,7 +8987,7 @@
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
     </row>
-    <row r="68" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B68" s="6" t="s">
         <v>16</v>
       </c>
@@ -9001,7 +9001,7 @@
       <c r="J68" s="6"/>
       <c r="K68" s="6"/>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B69" s="7" t="s">
         <v>12</v>
       </c>
@@ -9033,7 +9033,7 @@
         <v>-9.990000000000001E+307</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B70" s="10">
         <v>0</v>
       </c>
@@ -9074,7 +9074,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B71" s="10">
         <v>1</v>
       </c>
@@ -9115,7 +9115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B72" s="10">
         <v>-1</v>
       </c>
@@ -9156,7 +9156,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B73" s="10">
         <v>42.5</v>
       </c>
@@ -9197,7 +9197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B74" s="10">
         <v>-42.5</v>
       </c>
@@ -9238,7 +9238,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B75" s="12">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B76" s="12">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -9320,7 +9320,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B77" s="12">
         <v>9.990000000000001E+307</v>
       </c>
@@ -9361,7 +9361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B78" s="12">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
@@ -9414,7 +9414,7 @@
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
@@ -9426,7 +9426,7 @@
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
     </row>
-    <row r="81" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B81" s="6" t="s">
         <v>17</v>
       </c>
@@ -9440,7 +9440,7 @@
       <c r="J81" s="6"/>
       <c r="K81" s="6"/>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B82" s="7" t="s">
         <v>12</v>
       </c>
@@ -9472,7 +9472,7 @@
         <v>-9.990000000000001E+307</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B83" s="10">
         <v>0</v>
       </c>
@@ -9513,7 +9513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B84" s="10">
         <v>1</v>
       </c>
@@ -9554,7 +9554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="10">
         <v>-1</v>
       </c>
@@ -9595,7 +9595,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B86" s="10">
         <v>42.5</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B87" s="10">
         <v>-42.5</v>
       </c>
@@ -9677,7 +9677,7 @@
         <v>-42.5</v>
       </c>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B88" s="12">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -9718,7 +9718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="12">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -9759,7 +9759,7 @@
         <v>-9.9999999999999951E-308</v>
       </c>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="12">
         <v>9.990000000000001E+307</v>
       </c>
@@ -9800,7 +9800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B91" s="12">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -9841,7 +9841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
@@ -9853,7 +9853,7 @@
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
@@ -9865,7 +9865,7 @@
       <c r="J93" s="2"/>
       <c r="K93" s="2"/>
     </row>
-    <row r="94" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B94" s="6" t="s">
         <v>18</v>
       </c>
@@ -9879,7 +9879,7 @@
       <c r="J94" s="6"/>
       <c r="K94" s="6"/>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="7" t="s">
         <v>12</v>
       </c>
@@ -9911,7 +9911,7 @@
         <v>-9.990000000000001E+307</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B96" s="10">
         <v>0</v>
       </c>
@@ -9952,7 +9952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B97" s="10">
         <v>1</v>
       </c>
@@ -9993,7 +9993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B98" s="10">
         <v>-1</v>
       </c>
@@ -10034,7 +10034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B99" s="10">
         <v>42.5</v>
       </c>
@@ -10075,7 +10075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B100" s="10">
         <v>-42.5</v>
       </c>
@@ -10116,7 +10116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B101" s="12">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -10157,7 +10157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B102" s="12">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -10198,7 +10198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B103" s="12">
         <v>9.990000000000001E+307</v>
       </c>
@@ -10239,7 +10239,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B104" s="12">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -10280,7 +10280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
@@ -10292,7 +10292,7 @@
       <c r="J105" s="2"/>
       <c r="K105" s="2"/>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
@@ -10304,7 +10304,7 @@
       <c r="J106" s="2"/>
       <c r="K106" s="2"/>
     </row>
-    <row r="107" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B107" s="3" t="s">
         <v>19</v>
       </c>
@@ -10318,7 +10318,7 @@
       <c r="J107" s="3"/>
       <c r="K107" s="3"/>
     </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
@@ -10330,7 +10330,7 @@
       <c r="J108" s="2"/>
       <c r="K108" s="2"/>
     </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B109" s="13" t="s">
         <v>20</v>
       </c>
@@ -10344,7 +10344,7 @@
       <c r="J109" s="13"/>
       <c r="K109" s="13"/>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B110" s="10">
         <v>0</v>
       </c>
@@ -10385,7 +10385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B111" s="10">
         <v>1</v>
       </c>
@@ -10426,7 +10426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B112" s="10">
         <v>-1</v>
       </c>
@@ -10467,7 +10467,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B113" s="10">
         <v>42.5</v>
       </c>
@@ -10508,7 +10508,7 @@
         <v>1.4050061177528801E+51</v>
       </c>
     </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B114" s="10">
         <v>-42.5</v>
       </c>
@@ -10549,7 +10549,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B115" s="12">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -10590,7 +10590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B116" s="12">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -10631,7 +10631,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B117" s="12">
         <v>9.990000000000001E+307</v>
       </c>
@@ -10672,7 +10672,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B118" s="12">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
@@ -10725,7 +10725,7 @@
       <c r="J119" s="2"/>
       <c r="K119" s="2"/>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
@@ -10737,7 +10737,7 @@
       <c r="J120" s="2"/>
       <c r="K120" s="2"/>
     </row>
-    <row r="121" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B121" s="3" t="s">
         <v>21</v>
       </c>
@@ -10751,7 +10751,7 @@
       <c r="J121" s="3"/>
       <c r="K121" s="3"/>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
@@ -10763,7 +10763,7 @@
       <c r="J122" s="2"/>
       <c r="K122" s="2"/>
     </row>
-    <row r="123" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B123" s="6" t="s">
         <v>22</v>
       </c>
@@ -10777,7 +10777,7 @@
       <c r="J123" s="6"/>
       <c r="K123" s="6"/>
     </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B124" s="7" t="s">
         <v>23</v>
       </c>
@@ -10791,7 +10791,7 @@
       <c r="J124" s="14"/>
       <c r="K124" s="14"/>
     </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B125" s="10">
         <v>0</v>
       </c>
@@ -10820,7 +10820,7 @@
       <c r="J125" s="2"/>
       <c r="K125" s="2"/>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B126" s="10">
         <v>1</v>
       </c>
@@ -10849,7 +10849,7 @@
       <c r="J126" s="2"/>
       <c r="K126" s="2"/>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B127" s="10">
         <v>-1</v>
       </c>
@@ -10878,7 +10878,7 @@
       <c r="J127" s="2"/>
       <c r="K127" s="2"/>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B128" s="10">
         <v>42.5</v>
       </c>
@@ -10907,7 +10907,7 @@
       <c r="J128" s="2"/>
       <c r="K128" s="2"/>
     </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B129" s="10">
         <v>-42.5</v>
       </c>
@@ -10936,7 +10936,7 @@
       <c r="J129" s="2"/>
       <c r="K129" s="2"/>
     </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B130" s="12">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -10965,7 +10965,7 @@
       <c r="J130" s="2"/>
       <c r="K130" s="2"/>
     </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B131" s="12">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -10994,7 +10994,7 @@
       <c r="J131" s="2"/>
       <c r="K131" s="2"/>
     </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B132" s="12">
         <v>9.990000000000001E+307</v>
       </c>
@@ -11023,7 +11023,7 @@
       <c r="J132" s="2"/>
       <c r="K132" s="2"/>
     </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B133" s="12">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -11052,7 +11052,7 @@
       <c r="J133" s="2"/>
       <c r="K133" s="2"/>
     </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
@@ -11064,7 +11064,7 @@
       <c r="J134" s="2"/>
       <c r="K134" s="2"/>
     </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
@@ -11076,7 +11076,7 @@
       <c r="J135" s="2"/>
       <c r="K135" s="2"/>
     </row>
-    <row r="136" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B136" s="6" t="s">
         <v>24</v>
       </c>
@@ -11090,7 +11090,7 @@
       <c r="J136" s="6"/>
       <c r="K136" s="6"/>
     </row>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B137" s="7" t="s">
         <v>23</v>
       </c>
@@ -11104,7 +11104,7 @@
       <c r="J137" s="14"/>
       <c r="K137" s="14"/>
     </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B138" s="10">
         <v>0</v>
       </c>
@@ -11133,7 +11133,7 @@
       <c r="J138" s="2"/>
       <c r="K138" s="2"/>
     </row>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B139" s="10">
         <v>1</v>
       </c>
@@ -11162,7 +11162,7 @@
       <c r="J139" s="2"/>
       <c r="K139" s="2"/>
     </row>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B140" s="10">
         <v>-1</v>
       </c>
@@ -11191,7 +11191,7 @@
       <c r="J140" s="2"/>
       <c r="K140" s="2"/>
     </row>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B141" s="10">
         <v>42.5</v>
       </c>
@@ -11220,7 +11220,7 @@
       <c r="J141" s="2"/>
       <c r="K141" s="2"/>
     </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B142" s="10">
         <v>-42.5</v>
       </c>
@@ -11249,7 +11249,7 @@
       <c r="J142" s="2"/>
       <c r="K142" s="2"/>
     </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B143" s="12">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -11278,7 +11278,7 @@
       <c r="J143" s="2"/>
       <c r="K143" s="2"/>
     </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B144" s="12">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -11307,7 +11307,7 @@
       <c r="J144" s="2"/>
       <c r="K144" s="2"/>
     </row>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B145" s="12">
         <v>9.990000000000001E+307</v>
       </c>
@@ -11336,7 +11336,7 @@
       <c r="J145" s="2"/>
       <c r="K145" s="2"/>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B146" s="12">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -11365,7 +11365,7 @@
       <c r="J146" s="2"/>
       <c r="K146" s="2"/>
     </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
@@ -11377,7 +11377,7 @@
       <c r="J147" s="2"/>
       <c r="K147" s="2"/>
     </row>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
@@ -11389,7 +11389,7 @@
       <c r="J148" s="2"/>
       <c r="K148" s="2"/>
     </row>
-    <row r="149" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B149" s="6" t="s">
         <v>25</v>
       </c>
@@ -11403,7 +11403,7 @@
       <c r="J149" s="6"/>
       <c r="K149" s="6"/>
     </row>
-    <row r="150" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B150" s="7" t="s">
         <v>23</v>
       </c>
@@ -11417,7 +11417,7 @@
       <c r="J150" s="14"/>
       <c r="K150" s="14"/>
     </row>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B151" s="10">
         <v>0</v>
       </c>
@@ -11446,7 +11446,7 @@
       <c r="J151" s="2"/>
       <c r="K151" s="2"/>
     </row>
-    <row r="152" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B152" s="10">
         <v>1</v>
       </c>
@@ -11475,7 +11475,7 @@
       <c r="J152" s="2"/>
       <c r="K152" s="2"/>
     </row>
-    <row r="153" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B153" s="10">
         <v>-1</v>
       </c>
@@ -11504,7 +11504,7 @@
       <c r="J153" s="2"/>
       <c r="K153" s="2"/>
     </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B154" s="10">
         <v>42.5</v>
       </c>
@@ -11533,7 +11533,7 @@
       <c r="J154" s="2"/>
       <c r="K154" s="2"/>
     </row>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B155" s="10">
         <v>-42.5</v>
       </c>
@@ -11562,7 +11562,7 @@
       <c r="J155" s="2"/>
       <c r="K155" s="2"/>
     </row>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B156" s="12">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -11591,7 +11591,7 @@
       <c r="J156" s="2"/>
       <c r="K156" s="2"/>
     </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B157" s="12">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -11620,7 +11620,7 @@
       <c r="J157" s="2"/>
       <c r="K157" s="2"/>
     </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B158" s="12">
         <v>9.990000000000001E+307</v>
       </c>
@@ -11649,7 +11649,7 @@
       <c r="J158" s="2"/>
       <c r="K158" s="2"/>
     </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B159" s="12">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -11678,7 +11678,7 @@
       <c r="J159" s="2"/>
       <c r="K159" s="2"/>
     </row>
-    <row r="160" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
@@ -11690,7 +11690,7 @@
       <c r="J160" s="2"/>
       <c r="K160" s="2"/>
     </row>
-    <row r="161" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
@@ -11702,7 +11702,7 @@
       <c r="J161" s="2"/>
       <c r="K161" s="2"/>
     </row>
-    <row r="162" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B162" s="6" t="s">
         <v>26</v>
       </c>
@@ -11716,7 +11716,7 @@
       <c r="J162" s="6"/>
       <c r="K162" s="6"/>
     </row>
-    <row r="163" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B163" s="7" t="s">
         <v>27</v>
       </c>
@@ -11730,7 +11730,7 @@
       <c r="J163" s="14"/>
       <c r="K163" s="14"/>
     </row>
-    <row r="164" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B164" s="10">
         <v>0</v>
       </c>
@@ -11759,7 +11759,7 @@
       <c r="J164" s="2"/>
       <c r="K164" s="2"/>
     </row>
-    <row r="165" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B165" s="10">
         <v>1</v>
       </c>
@@ -11788,7 +11788,7 @@
       <c r="J165" s="2"/>
       <c r="K165" s="2"/>
     </row>
-    <row r="166" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B166" s="10">
         <v>-1</v>
       </c>
@@ -11817,7 +11817,7 @@
       <c r="J166" s="2"/>
       <c r="K166" s="2"/>
     </row>
-    <row r="167" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <v>42.5</v>
       </c>
@@ -11846,7 +11846,7 @@
       <c r="J167" s="2"/>
       <c r="K167" s="2"/>
     </row>
-    <row r="168" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B168" s="10">
         <v>-42.5</v>
       </c>
@@ -11875,7 +11875,7 @@
       <c r="J168" s="2"/>
       <c r="K168" s="2"/>
     </row>
-    <row r="169" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B169" s="12">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -11904,7 +11904,7 @@
       <c r="J169" s="2"/>
       <c r="K169" s="2"/>
     </row>
-    <row r="170" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B170" s="12">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -11933,7 +11933,7 @@
       <c r="J170" s="2"/>
       <c r="K170" s="2"/>
     </row>
-    <row r="171" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B171" s="12">
         <v>9.990000000000001E+307</v>
       </c>
@@ -11962,7 +11962,7 @@
       <c r="J171" s="2"/>
       <c r="K171" s="2"/>
     </row>
-    <row r="172" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B172" s="12">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -11991,7 +11991,7 @@
       <c r="J172" s="2"/>
       <c r="K172" s="2"/>
     </row>
-    <row r="173" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
@@ -12003,7 +12003,7 @@
       <c r="J173" s="2"/>
       <c r="K173" s="2"/>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
@@ -12015,7 +12015,7 @@
       <c r="J174" s="2"/>
       <c r="K174" s="2"/>
     </row>
-    <row r="175" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B175" s="6" t="s">
         <v>28</v>
       </c>
@@ -12029,7 +12029,7 @@
       <c r="J175" s="6"/>
       <c r="K175" s="6"/>
     </row>
-    <row r="176" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="176" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B176" s="7" t="s">
         <v>27</v>
       </c>
@@ -12043,7 +12043,7 @@
       <c r="J176" s="14"/>
       <c r="K176" s="14"/>
     </row>
-    <row r="177" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B177" s="10">
         <v>0</v>
       </c>
@@ -12072,7 +12072,7 @@
       <c r="J177" s="2"/>
       <c r="K177" s="2"/>
     </row>
-    <row r="178" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B178" s="10">
         <v>1</v>
       </c>
@@ -12101,7 +12101,7 @@
       <c r="J178" s="2"/>
       <c r="K178" s="2"/>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B179" s="10">
         <v>-1</v>
       </c>
@@ -12130,7 +12130,7 @@
       <c r="J179" s="2"/>
       <c r="K179" s="2"/>
     </row>
-    <row r="180" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B180" s="10">
         <v>42.5</v>
       </c>
@@ -12159,7 +12159,7 @@
       <c r="J180" s="2"/>
       <c r="K180" s="2"/>
     </row>
-    <row r="181" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B181" s="10">
         <v>-42.5</v>
       </c>
@@ -12188,7 +12188,7 @@
       <c r="J181" s="2"/>
       <c r="K181" s="2"/>
     </row>
-    <row r="182" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B182" s="12">
         <v>9.9999999999999991E-308</v>
       </c>
@@ -12217,7 +12217,7 @@
       <c r="J182" s="2"/>
       <c r="K182" s="2"/>
     </row>
-    <row r="183" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B183" s="12">
         <v>-9.9999999999999991E-308</v>
       </c>
@@ -12246,7 +12246,7 @@
       <c r="J183" s="2"/>
       <c r="K183" s="2"/>
     </row>
-    <row r="184" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B184" s="12">
         <v>9.990000000000001E+307</v>
       </c>
@@ -12275,7 +12275,7 @@
       <c r="J184" s="2"/>
       <c r="K184" s="2"/>
     </row>
-    <row r="185" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B185" s="12">
         <v>-9.990000000000001E+307</v>
       </c>
@@ -12304,7 +12304,7 @@
       <c r="J185" s="2"/>
       <c r="K185" s="2"/>
     </row>
-    <row r="186" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
@@ -12316,7 +12316,7 @@
       <c r="J186" s="2"/>
       <c r="K186" s="2"/>
     </row>
-    <row r="187" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
@@ -12328,7 +12328,7 @@
       <c r="J187" s="2"/>
       <c r="K187" s="2"/>
     </row>
-    <row r="188" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
@@ -12340,12 +12340,12 @@
       <c r="J188" s="2"/>
       <c r="K188" s="2"/>
     </row>
-    <row r="190" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B190" s="15" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="191" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="191" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B191" s="16" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -12353,7 +12353,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="192" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="192" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B192" s="16" t="e">
         <v>#NUM!</v>
       </c>
@@ -12361,7 +12361,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="193" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="193" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B193" s="16" t="e">
         <v>#VALUE!</v>
       </c>
@@ -12369,7 +12369,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="194" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="194" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B194" s="16" t="s">
         <v>33</v>
       </c>
@@ -12377,7 +12377,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="1109" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="1109" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C1109" s="18" t="s">
         <v>35</v>
       </c>
@@ -12406,7 +12406,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="1124" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="1124" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C1124" s="18">
         <v>-2</v>
       </c>
@@ -12423,7 +12423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1137" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="1137" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C1137" s="18">
         <v>-2</v>
       </c>
@@ -12440,7 +12440,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1150" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="1150" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C1150" s="18">
         <v>-2</v>
       </c>
@@ -12457,7 +12457,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1163" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="1163" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C1163" s="18">
         <v>1</v>
       </c>
@@ -12474,7 +12474,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="1176" spans="3:7" x14ac:dyDescent="0.2">
+    <row r="1176" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C1176" s="18">
         <v>1</v>
       </c>
